--- a/output/pdf_financials_xlsx/FINX.xlsx
+++ b/output/pdf_financials_xlsx/FINX.xlsx
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.386579</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.850503</v>
       </c>
     </row>
     <row r="93">
@@ -2602,7 +2602,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
         <v>0.386579</v>
       </c>

--- a/output/pdf_financials_xlsx/FINX.xlsx
+++ b/output/pdf_financials_xlsx/FINX.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.218484</v>
+        <v>0.45432</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.695716</v>
+        <v>1.408136</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.218484</v>
+        <v>-0.45432</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.695716</v>
+        <v>-1.408136</v>
       </c>
     </row>
     <row r="12">
@@ -3814,14 +3814,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
-        <v>-0.45432</v>
+        <v>0.45432</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-1.408136</v>
+        <v>1.408136</v>
       </c>
     </row>
     <row r="60">

--- a/output/pdf_financials_xlsx/FINX.xlsx
+++ b/output/pdf_financials_xlsx/FINX.xlsx
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007237</v>
       </c>
     </row>
     <row r="112">
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007237</v>
       </c>
     </row>
     <row r="135">
@@ -2207,7 +2207,7 @@
         <v>-0.278109</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.296671</v>
+        <v>-1.303908</v>
       </c>
     </row>
   </sheetData>
@@ -3008,7 +3008,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -3062,7 +3066,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>1.162645</v>
       </c>
